--- a/AutoRappel_Emmaus-Connect-main/test/Rapport inscription bénéficiaire 30 jour.xlsx
+++ b/AutoRappel_Emmaus-Connect-main/test/Rapport inscription bénéficiaire 30 jour.xlsx
@@ -984,7 +984,9 @@
         </is>
       </c>
       <c r="F18" s="30" t="n"/>
-      <c r="Z18" s="21" t="n"/>
+      <c r="Z18" s="21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="22">
       <c r="A19" s="29" t="n"/>
